--- a/Electricals/Pinouts/LattePanda_Mu_Ultra_Edge_Connector_Pinout.xlsx
+++ b/Electricals/Pinouts/LattePanda_Mu_Ultra_Edge_Connector_Pinout.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\LP新开项目\Mu Ultra\docs资料梳理\已审阅\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\LattePanda-Mu-Ultra\Electricals\Pinouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="348">
   <si>
     <r>
       <rPr>
@@ -88,7 +88,16 @@
     <t>This document is applicable only to LattePanda Mu Ultra compute modules equipped with Intel Core Ultra 2 Series processor(Lunar Lake).</t>
   </si>
   <si>
-    <t>Due to the large number of pins that serve multiple functions, please consult the BIOS functionality documentation before beginning your design.</t>
+    <t>Due to the various PCIe bifurcation, please consult the BIOS functionality documentation before beginning your design:</t>
+  </si>
+  <si>
+    <t>https://github.com/LattePandaTeam/LattePanda-Mu-Ultra/tree/main/Softwares/BIOS</t>
+  </si>
+  <si>
+    <t>Pinout Description Page</t>
+  </si>
+  <si>
+    <t>https://github.com/LattePandaTeam/LattePanda-Mu-Ultra/tree/main/Electricals/Pinouts</t>
   </si>
   <si>
     <t>Pin</t>
@@ -386,7 +395,7 @@
     <t>USB 2.0 Port 1 Differential Pair</t>
   </si>
   <si>
-    <t>Bind and Use with TCP Port 1 in Default BIOS</t>
+    <t>Bound to TCP1 in Default BIOS</t>
   </si>
   <si>
     <t>USB2_P1_P</t>
@@ -872,16 +881,16 @@
     <t>USB2_P5_N</t>
   </si>
   <si>
-    <t>USB2_P6_P (BT Only)</t>
+    <t>USB2_P6_P</t>
   </si>
   <si>
     <t>USB 2.0 Port 6 Differential Pair</t>
   </si>
   <si>
-    <t>Only for Wireless Module's Bluetooth, Not for Generic USB 2.0</t>
-  </si>
-  <si>
-    <t>USB2_P6_N (BT Only)</t>
+    <t>Dedicated to BT; can also for generic USB 2.0</t>
+  </si>
+  <si>
+    <t>USB2_P6_N</t>
   </si>
   <si>
     <t>REFCLK3_P</t>
@@ -938,7 +947,7 @@
     <t>USB 2.0 Port 2 Differential Pair</t>
   </si>
   <si>
-    <t>Bind and Use with TCP Port 0 in Default BIOS</t>
+    <t>Bound to TCP0 in Default BIOS</t>
   </si>
   <si>
     <t>USB2_P2_N</t>
@@ -1161,9 +1170,6 @@
   </si>
   <si>
     <t>TCP1_AUX_N</t>
-  </si>
-  <si>
-    <t>VDC</t>
   </si>
 </sst>
 </file>
@@ -1217,7 +1223,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0B5FD1"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1225,7 +1231,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF0B5FD1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1699,7 +1705,7 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1829,7 +1835,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1875,7 +1881,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2187,8 +2196,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4520565" y="781050"/>
-          <a:ext cx="304800" cy="295275"/>
+          <a:off x="4800600" y="838200"/>
+          <a:ext cx="304800" cy="304800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2229,8 +2238,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1905" y="1715135"/>
-          <a:ext cx="10029825" cy="4530725"/>
+          <a:off x="1905" y="1838960"/>
+          <a:ext cx="10629900" cy="4987925"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2492,23 +2501,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:H16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
+  <dimension ref="B2:H35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" ht="15.75" spans="2:8">
+    <row r="2" spans="2:8">
       <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="15.75" spans="2:8">
+    <row r="3" spans="2:8">
       <c r="B3" s="14" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="15.75" spans="2:8">
+    <row r="5" spans="2:8">
       <c r="B5" s="14" t="s">
         <v>2</v>
       </c>
@@ -2525,12 +2534,28 @@
       </c>
     </row>
     <row r="8" spans="2:8">
-      <c r="B8" s="15"/>
+      <c r="B8" s="15" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" spans="2:8">
-      <c r="B16" s="15"/>
+      <c r="B16" s="16"/>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="15" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B8" r:id="rId2" display="https://github.com/LattePandaTeam/LattePanda-Mu-Ultra/tree/main/Softwares/BIOS"/>
+    <hyperlink ref="B35" r:id="rId3" display="https://github.com/LattePandaTeam/LattePanda-Mu-Ultra/tree/main/Electricals/Pinouts"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
@@ -2541,39 +2566,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G132"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="4.87610619469027" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7522123893805" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.2477876106195" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.3716814159292" style="2" customWidth="1"/>
-    <col min="5" max="5" width="61.8761061946903" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.3716814159292" style="2" customWidth="1"/>
-    <col min="7" max="7" width="50.2477876106195" style="2" customWidth="1"/>
+    <col min="1" max="1" width="4.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="61.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="50.25" style="2" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:7">
+    <row r="1" spans="1:7">
       <c r="A1" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2581,22 +2606,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2604,22 +2629,22 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2627,22 +2652,22 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2650,22 +2675,22 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2673,19 +2698,19 @@
         <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2693,19 +2718,19 @@
         <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2713,22 +2738,22 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2736,22 +2761,22 @@
         <v>15</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2759,19 +2784,19 @@
         <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2779,22 +2804,22 @@
         <v>19</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2802,22 +2827,22 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2825,19 +2850,19 @@
         <v>23</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2845,22 +2870,22 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2868,22 +2893,22 @@
         <v>27</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2891,19 +2916,19 @@
         <v>29</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2911,22 +2936,22 @@
         <v>31</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2934,22 +2959,22 @@
         <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2957,19 +2982,19 @@
         <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2977,22 +3002,22 @@
         <v>37</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3000,22 +3025,22 @@
         <v>39</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3023,19 +3048,19 @@
         <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3043,22 +3068,22 @@
         <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3066,22 +3091,22 @@
         <v>45</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3089,19 +3114,19 @@
         <v>47</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3109,22 +3134,22 @@
         <v>49</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3132,22 +3157,22 @@
         <v>51</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3155,19 +3180,19 @@
         <v>53</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3175,22 +3200,22 @@
         <v>55</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3198,22 +3223,22 @@
         <v>57</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3221,19 +3246,19 @@
         <v>59</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3241,22 +3266,22 @@
         <v>61</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3264,22 +3289,22 @@
         <v>63</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3287,19 +3312,19 @@
         <v>65</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3307,22 +3332,22 @@
         <v>67</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3330,22 +3355,22 @@
         <v>69</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -3353,19 +3378,19 @@
         <v>71</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3373,19 +3398,19 @@
         <v>73</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3393,19 +3418,19 @@
         <v>75</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="D39" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3413,19 +3438,19 @@
         <v>77</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3433,19 +3458,19 @@
         <v>79</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="E41" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3453,19 +3478,19 @@
         <v>81</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3473,19 +3498,19 @@
         <v>83</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3493,22 +3518,22 @@
         <v>85</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3516,22 +3541,22 @@
         <v>87</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3539,19 +3564,19 @@
         <v>89</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3559,22 +3584,22 @@
         <v>91</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E47" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3582,22 +3607,22 @@
         <v>93</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E48" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3605,19 +3630,19 @@
         <v>95</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -3625,22 +3650,22 @@
         <v>97</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3648,22 +3673,22 @@
         <v>99</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3671,19 +3696,19 @@
         <v>101</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3691,22 +3716,22 @@
         <v>103</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3714,22 +3739,22 @@
         <v>105</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3737,19 +3762,19 @@
         <v>107</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3757,22 +3782,22 @@
         <v>109</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3780,22 +3805,22 @@
         <v>111</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3803,19 +3828,19 @@
         <v>113</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3823,19 +3848,19 @@
         <v>115</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3843,22 +3868,22 @@
         <v>117</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3866,22 +3891,22 @@
         <v>119</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3889,19 +3914,19 @@
         <v>121</v>
       </c>
       <c r="B62" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C62" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>100</v>
-      </c>
       <c r="E62" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63" s="8" customFormat="1" spans="1:7">
@@ -3909,22 +3934,22 @@
         <v>123</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3932,22 +3957,22 @@
         <v>125</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3955,22 +3980,22 @@
         <v>127</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3978,22 +4003,22 @@
         <v>129</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -4001,45 +4026,45 @@
         <v>131</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="68" ht="30" spans="1:7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="68" ht="33" spans="1:7">
       <c r="A68" s="1">
         <v>133</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -4047,19 +4072,19 @@
         <v>135</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4067,22 +4092,22 @@
         <v>137</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -4090,22 +4115,22 @@
         <v>139</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -4113,22 +4138,22 @@
         <v>141</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G72" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -4136,27 +4161,27 @@
         <v>143</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B74" s="10"/>
       <c r="C74" s="11"/>
@@ -4170,22 +4195,22 @@
         <v>145</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -4193,22 +4218,22 @@
         <v>147</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -4216,19 +4241,19 @@
         <v>149</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -4236,19 +4261,19 @@
         <v>151</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -4256,19 +4281,19 @@
         <v>153</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -4276,19 +4301,19 @@
         <v>155</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -4296,19 +4321,19 @@
         <v>157</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -4316,19 +4341,19 @@
         <v>159</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -4336,19 +4361,19 @@
         <v>161</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -4356,19 +4381,19 @@
         <v>163</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -4376,19 +4401,19 @@
         <v>165</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4396,19 +4421,19 @@
         <v>167</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4416,22 +4441,22 @@
         <v>169</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="88" ht="17.1" customHeight="1" spans="1:7">
@@ -4439,22 +4464,22 @@
         <v>171</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4462,22 +4487,22 @@
         <v>173</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4485,22 +4510,22 @@
         <v>175</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4508,22 +4533,22 @@
         <v>177</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4531,22 +4556,22 @@
         <v>179</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -4554,19 +4579,19 @@
         <v>181</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -4574,19 +4599,19 @@
         <v>183</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -4594,19 +4619,19 @@
         <v>185</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4614,19 +4639,19 @@
         <v>187</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4634,19 +4659,19 @@
         <v>189</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4654,19 +4679,19 @@
         <v>191</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4674,19 +4699,19 @@
         <v>193</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4694,19 +4719,19 @@
         <v>195</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4714,22 +4739,22 @@
         <v>197</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4737,22 +4762,22 @@
         <v>199</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4760,19 +4785,19 @@
         <v>201</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4780,22 +4805,22 @@
         <v>203</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D104" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="C104" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D104" s="8" t="s">
-        <v>171</v>
-      </c>
       <c r="E104" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4803,22 +4828,22 @@
         <v>205</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4826,19 +4851,19 @@
         <v>207</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4846,22 +4871,22 @@
         <v>209</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4869,22 +4894,22 @@
         <v>211</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4892,19 +4917,19 @@
         <v>213</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4912,22 +4937,22 @@
         <v>215</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4935,22 +4960,22 @@
         <v>217</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4958,19 +4983,19 @@
         <v>219</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4978,19 +5003,19 @@
         <v>221</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4998,19 +5023,19 @@
         <v>223</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -5018,19 +5043,19 @@
         <v>225</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -5038,22 +5063,22 @@
         <v>227</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -5061,22 +5086,22 @@
         <v>229</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -5084,19 +5109,19 @@
         <v>231</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -5104,22 +5129,22 @@
         <v>233</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5127,22 +5152,22 @@
         <v>235</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D120" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -5150,19 +5175,19 @@
         <v>237</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -5170,22 +5195,22 @@
         <v>239</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -5193,22 +5218,22 @@
         <v>241</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -5216,19 +5241,19 @@
         <v>243</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -5236,22 +5261,22 @@
         <v>245</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -5259,22 +5284,22 @@
         <v>247</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -5282,19 +5307,19 @@
         <v>249</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -5302,19 +5327,19 @@
         <v>251</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -5322,19 +5347,19 @@
         <v>253</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -5342,19 +5367,19 @@
         <v>255</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -5362,19 +5387,19 @@
         <v>257</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -5382,19 +5407,19 @@
         <v>259</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -5410,41 +5435,41 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G132"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="4.75221238938053" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.8761061946903" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.2743362831858" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.3716814159292" style="2" customWidth="1"/>
-    <col min="5" max="5" width="61.6283185840708" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.6283185840708" style="2" customWidth="1"/>
-    <col min="7" max="7" width="49.6283185840708" style="2" customWidth="1"/>
+    <col min="1" max="1" width="4.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.275" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="61.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="49.625" style="2" customWidth="1"/>
     <col min="8" max="9" width="9" style="2"/>
-    <col min="10" max="10" width="11.5044247787611" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.5083333333333" style="2" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:7">
+    <row r="1" spans="1:7">
       <c r="A1" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5452,22 +5477,22 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -5475,19 +5500,19 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -5495,22 +5520,22 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -5518,19 +5543,19 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -5538,19 +5563,19 @@
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -5558,19 +5583,19 @@
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -5578,19 +5603,19 @@
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -5598,22 +5623,22 @@
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -5621,22 +5646,22 @@
         <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -5644,19 +5669,19 @@
         <v>20</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -5664,22 +5689,22 @@
         <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -5687,22 +5712,22 @@
         <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -5710,19 +5735,19 @@
         <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -5730,22 +5755,22 @@
         <v>28</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -5753,22 +5778,22 @@
         <v>30</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -5776,19 +5801,19 @@
         <v>32</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -5796,22 +5821,22 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -5819,22 +5844,22 @@
         <v>36</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -5842,19 +5867,19 @@
         <v>38</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -5862,22 +5887,22 @@
         <v>40</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -5885,22 +5910,22 @@
         <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -5908,19 +5933,19 @@
         <v>44</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -5928,22 +5953,22 @@
         <v>46</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -5951,22 +5976,22 @@
         <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -5974,19 +5999,19 @@
         <v>50</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -5994,22 +6019,22 @@
         <v>52</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -6017,22 +6042,22 @@
         <v>54</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -6040,19 +6065,19 @@
         <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -6060,22 +6085,22 @@
         <v>58</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -6083,22 +6108,22 @@
         <v>60</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -6106,19 +6131,19 @@
         <v>62</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -6126,22 +6151,22 @@
         <v>64</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -6149,22 +6174,22 @@
         <v>66</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -6172,19 +6197,19 @@
         <v>68</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -6192,22 +6217,22 @@
         <v>70</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -6215,22 +6240,22 @@
         <v>72</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -6238,19 +6263,19 @@
         <v>74</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -6258,19 +6283,19 @@
         <v>76</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -6278,19 +6303,19 @@
         <v>78</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -6298,19 +6323,19 @@
         <v>80</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -6318,22 +6343,22 @@
         <v>82</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -6341,22 +6366,22 @@
         <v>84</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -6364,19 +6389,19 @@
         <v>86</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -6384,22 +6409,22 @@
         <v>88</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -6407,22 +6432,22 @@
         <v>90</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -6430,19 +6455,19 @@
         <v>92</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -6450,22 +6475,22 @@
         <v>94</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -6473,22 +6498,22 @@
         <v>96</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -6496,19 +6521,19 @@
         <v>98</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -6516,22 +6541,22 @@
         <v>100</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -6539,22 +6564,22 @@
         <v>102</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -6562,22 +6587,22 @@
         <v>104</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -6585,22 +6610,22 @@
         <v>106</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -6608,22 +6633,22 @@
         <v>108</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -6631,19 +6656,19 @@
         <v>110</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -6651,22 +6676,22 @@
         <v>112</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -6674,22 +6699,22 @@
         <v>114</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -6697,19 +6722,19 @@
         <v>116</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -6717,19 +6742,19 @@
         <v>118</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -6737,19 +6762,19 @@
         <v>120</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -6757,19 +6782,19 @@
         <v>122</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -6777,19 +6802,19 @@
         <v>124</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -6797,19 +6822,19 @@
         <v>126</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -6817,19 +6842,19 @@
         <v>128</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -6837,22 +6862,22 @@
         <v>130</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -6860,19 +6885,19 @@
         <v>132</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -6880,22 +6905,22 @@
         <v>134</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -6903,19 +6928,19 @@
         <v>136</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -6923,19 +6948,19 @@
         <v>138</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -6943,19 +6968,19 @@
         <v>140</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -6963,19 +6988,19 @@
         <v>142</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -6983,24 +7008,24 @@
         <v>144</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B74" s="10"/>
       <c r="C74" s="11"/>
@@ -7014,22 +7039,22 @@
         <v>146</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -7037,22 +7062,22 @@
         <v>148</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -7060,22 +7085,22 @@
         <v>150</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -7083,22 +7108,22 @@
         <v>152</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -7106,22 +7131,22 @@
         <v>154</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -7129,22 +7154,22 @@
         <v>156</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -7152,19 +7177,19 @@
         <v>158</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -7172,19 +7197,19 @@
         <v>160</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -7192,19 +7217,19 @@
         <v>162</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -7212,19 +7237,19 @@
         <v>164</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -7232,19 +7257,19 @@
         <v>166</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -7252,19 +7277,19 @@
         <v>168</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -7272,19 +7297,19 @@
         <v>170</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -7292,19 +7317,19 @@
         <v>172</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -7312,19 +7337,19 @@
         <v>174</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -7332,19 +7357,19 @@
         <v>176</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -7352,19 +7377,19 @@
         <v>178</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -7372,19 +7397,19 @@
         <v>180</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -7392,19 +7417,19 @@
         <v>182</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -7412,19 +7437,19 @@
         <v>184</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -7432,19 +7457,19 @@
         <v>186</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -7452,19 +7477,19 @@
         <v>188</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -7472,19 +7497,19 @@
         <v>190</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -7492,19 +7517,19 @@
         <v>192</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -7512,19 +7537,19 @@
         <v>194</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -7532,19 +7557,19 @@
         <v>196</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -7552,19 +7577,19 @@
         <v>198</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -7572,19 +7597,19 @@
         <v>200</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -7592,19 +7617,19 @@
         <v>202</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -7612,19 +7637,19 @@
         <v>204</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E104" s="8" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -7632,19 +7657,19 @@
         <v>206</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -7652,19 +7677,19 @@
         <v>208</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -7672,19 +7697,19 @@
         <v>210</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -7692,19 +7717,19 @@
         <v>212</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -7712,19 +7737,19 @@
         <v>214</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -7732,19 +7757,19 @@
         <v>216</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -7752,19 +7777,19 @@
         <v>218</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -7772,22 +7797,22 @@
         <v>220</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -7795,22 +7820,22 @@
         <v>222</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -7818,19 +7843,19 @@
         <v>224</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -7838,22 +7863,22 @@
         <v>226</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -7861,22 +7886,22 @@
         <v>228</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -7884,19 +7909,19 @@
         <v>230</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -7904,22 +7929,22 @@
         <v>232</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -7927,22 +7952,22 @@
         <v>234</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -7950,19 +7975,19 @@
         <v>236</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D120" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -7970,22 +7995,22 @@
         <v>238</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -7993,22 +8018,22 @@
         <v>240</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -8016,19 +8041,19 @@
         <v>242</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -8036,19 +8061,19 @@
         <v>244</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -8056,19 +8081,19 @@
         <v>246</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -8076,19 +8101,19 @@
         <v>248</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -8096,19 +8121,19 @@
         <v>250</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>345</v>
+        <v>201</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -8116,19 +8141,19 @@
         <v>252</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>345</v>
+        <v>201</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -8136,19 +8161,19 @@
         <v>254</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>345</v>
+        <v>201</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -8156,19 +8181,19 @@
         <v>256</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>345</v>
+        <v>201</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -8176,19 +8201,19 @@
         <v>258</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>345</v>
+        <v>201</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -8196,19 +8221,19 @@
         <v>260</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>345</v>
+        <v>201</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
